--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260510_203733.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
